--- a/FileIndexingAndManagement-main/uploads/exported_files.xlsx
+++ b/FileIndexingAndManagement-main/uploads/exported_files.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,44 +463,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Railway</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>f123</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>FC001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>doc1.pdf</t>
+          <t>image1.png</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC001</t>
+          <t>FC002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -508,22 +492,6 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>image1.png</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FC002</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FileIndexingAndManagement-main/uploads/exported_files.xlsx
+++ b/FileIndexingAndManagement-main/uploads/exported_files.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>doc1.pdf</t>
+          <t>image1.png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FC001</t>
+          <t>FC002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -479,18 +479,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>image1.png</t>
+          <t>doc1.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FC002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>FC001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>establishment file</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
